--- a/stufe-5/icu/migrate-ig-ptdata--1967/observations-summary.xlsx
+++ b/stufe-5/icu/migrate-ig-ptdata--1967/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="145">
   <si>
     <t>Profile</t>
   </si>
@@ -47,55 +47,406 @@
     <t>Method</t>
   </si>
   <si>
-    <t>ISiKAlkoholAbusus</t>
-  </si>
-  <si>
-    <t>ISiK Alkohol Abusus</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#social-history</t>
+    <t>ISiKAtemfrequenz</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>null#15167005, null#74043-1</t>
+    <t>null#9279-1, null#null, null#151562</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>ISiKBlutdruckSystemischArteriell</t>
+  </si>
+  <si>
+    <t>null#85354-9, null#75367002, null#150016</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6, ISO 11073-10101 Health informatics - Point-of-care#150017, SNOMED CT#271649006</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4, ISO 11073-10101 Health informatics - Point-of-care#150018, SNOMED CT#271650006</t>
+  </si>
+  <si>
+    <t>LOINC#8478-0, ISO 11073-10101 Health informatics - Point-of-care#150019, SNOMED CT#6797001</t>
+  </si>
+  <si>
+    <t>ISiKEKG</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#procedure</t>
+  </si>
+  <si>
+    <t>null#11524-6, null#106073009</t>
+  </si>
+  <si>
+    <t>dateTimeĵ</t>
+  </si>
+  <si>
+    <t>SampledDataĵ</t>
+  </si>
+  <si>
+    <t>ISiKGCS</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#survey</t>
+  </si>
+  <si>
+    <t>null#9269-2, null#248241002, null#153728</t>
+  </si>
+  <si>
+    <t>LOINC#9267-6</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>LOINC#9268-4</t>
+  </si>
+  <si>
+    <t>LOINC#9270-0</t>
+  </si>
+  <si>
+    <t>ISiKHerzfrequenz</t>
+  </si>
+  <si>
+    <t>null#8867-4, null#null, null#147842</t>
+  </si>
+  <si>
+    <t>ISiKKoerpergewicht</t>
+  </si>
+  <si>
+    <t>null#29463-7, null#8339-4, null#null, null#188736</t>
+  </si>
+  <si>
+    <t>ISiKKoerpergroesse</t>
+  </si>
+  <si>
+    <t>null#8302-2, null#89269-5, null#null, null#188740</t>
+  </si>
+  <si>
+    <t>ISiKKoerperkerntemperatur</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#null, null#150364, null#150368, null#8329-5</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/isik/ValueSet/ISiKSpecificKernTempLoincVS (required)</t>
+  </si>
+  <si>
+    <t>ISiKKoerpertemperatur</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#null, null#150364</t>
+  </si>
+  <si>
+    <t>ISiKKopfumfang</t>
+  </si>
+  <si>
+    <t>null#9843-4, null#null, null#153856</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchung</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#laboratory</t>
+  </si>
+  <si>
+    <t>null#null</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
-    <t>dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>ISiKRaucherStatus</t>
-  </si>
-  <si>
-    <t>ISiK Raucherstatus</t>
-  </si>
-  <si>
-    <t>null#77176002, null#72166-2</t>
-  </si>
-  <si>
-    <t>ISiKSchwangerschaftsstatus</t>
-  </si>
-  <si>
-    <t>ISiK Schwangerschaftsstatus</t>
-  </si>
-  <si>
-    <t>LOINC#82810-3</t>
-  </si>
-  <si>
-    <t>ISiKStillstatus</t>
-  </si>
-  <si>
-    <t>null#413712001, null#63895-7</t>
+    <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungCRP</t>
+  </si>
+  <si>
+    <t>null#null, null#55235003</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungGFR</t>
+  </si>
+  <si>
+    <t>null#null, null#80274001</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungHb</t>
+  </si>
+  <si>
+    <t>null#null, null#416125006</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungPCT</t>
+  </si>
+  <si>
+    <t>null#null, null#418752001</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungSerumkreatinin</t>
+  </si>
+  <si>
+    <t>null#null, null#70901006</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungThrombozyten</t>
+  </si>
+  <si>
+    <t>null#null, null#365632008</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungTroponin</t>
+  </si>
+  <si>
+    <t>null#null, null#105000003</t>
+  </si>
+  <si>
+    <t>ISiKLaboruntersuchungTSH</t>
+  </si>
+  <si>
+    <t>null#null, null#61167004</t>
+  </si>
+  <si>
+    <t>ISiKSauerstoffsaettigungArteriell</t>
+  </si>
+  <si>
+    <t>null#2708-6, null#null, null#59408-5, null#150324</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-ideales-koerpergewicht</t>
+  </si>
+  <si>
+    <t>SD MII ICU Ideales Koerpergewicht</t>
+  </si>
+  <si>
+    <t>null#170804003, null#50064-5, null#188796</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-intrakranieller-druck-icp</t>
+  </si>
+  <si>
+    <t>SD MII ICU Intrakranieller Druck ICP</t>
+  </si>
+  <si>
+    <t>null#250844005, null#60956-0, null#153608</t>
+  </si>
+  <si>
+    <t>SNOMED CT#731998000</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpergewicht-percentil-altersabhaengig</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpergewicht Percentil Altersabhaengig</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs, SNOMED CT#248326004</t>
+  </si>
+  <si>
+    <t>null#1153592008, null#8336-0, null#null</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpergroesse-percentil-altersabhaengig</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpergroesse Percentil</t>
+  </si>
+  <si>
+    <t>null#1153605006, null#null, null#null</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-achsel</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Achsel</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#415882003, null#150364, null#150368, null#8329-5, null#8328-7, null#188452</t>
+  </si>
+  <si>
+    <t>SNOMED CT#91470000</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-gelenk</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Gelenk</t>
+  </si>
+  <si>
+    <t>null#250124002, null#8310-5, null#null</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/isik/ValueSet/ISiKSpecificGenericTempLoincVS (required)</t>
+  </si>
+  <si>
+    <t>SNOMED CT#39352004</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-generisch</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Generisch</t>
+  </si>
+  <si>
+    <t>null#null, null#8310-5, null#null</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-harnblase</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Harnblase</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#698832009, null#150364, null#150368, null#8329-5, null#8334-5, null#null</t>
+  </si>
+  <si>
+    <t>SNOMED CT#89837001</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-kern</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Kern</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#276885007, null#150364, null#150368, null#8329-5</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-leiste</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Leiste</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#415929009, null#150364, null#150368, null#8329-5, null#104063-3, null#null</t>
+  </si>
+  <si>
+    <t>SNOMED CT#26893007</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-nasal</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur nasal</t>
+  </si>
+  <si>
+    <t>null#null, null#8310-5, null#188504, null#76010-8</t>
+  </si>
+  <si>
+    <t>SNOMED CT#45206002</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-rektal</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur rektal</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#307047009, null#150364, null#150368, null#8329-5, null#8332-9, null#188420</t>
+  </si>
+  <si>
+    <t>SNOMED CT#34402009</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-stirn</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Stirn</t>
+  </si>
+  <si>
+    <t>null#415922000, null#8310-5, null#null</t>
+  </si>
+  <si>
+    <t>SNOMED CT#52795006</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-trommelfell</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur Trommelfell</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#415974002, null#150364, null#150368, null#8329-5, null#8333-7, null#150392</t>
+  </si>
+  <si>
+    <t>SNOMED CT#42859004</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-unter-der-zunge</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur unter der Zunge</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#415945006, null#150364, null#150368, null#8329-5, null#8331-1, null#188424</t>
+  </si>
+  <si>
+    <t>SNOMED CT#123851003</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-koerpertemperatur-vaginal</t>
+  </si>
+  <si>
+    <t>SD MII ICU Koerpertemperatur vaginal</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#364246006, null#150364, null#150368, null#8329-5, null#null, null#null</t>
+  </si>
+  <si>
+    <t>SNOMED CT#76784001</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-monitoring-und-vitaldaten</t>
+  </si>
+  <si>
+    <t>SD MII ICU Monitoring und Vitaldaten</t>
+  </si>
+  <si>
+    <t>null#null, null#null, null#null</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-o2saettigung-im-arteriellen-blut-durch-pulsoxymetrie</t>
+  </si>
+  <si>
+    <t>SD MII ICU Sauerstoffsaettigung Im Arteriellen Blut Durch Pulsoxymetrie</t>
+  </si>
+  <si>
+    <t>null#442476006, null#59408-5, null#150324, null#2708-6</t>
+  </si>
+  <si>
+    <t>SNOMED CT#11527006</t>
+  </si>
+  <si>
+    <t>sd-mii-icu-puls</t>
+  </si>
+  <si>
+    <t>SD MII ICU Puls</t>
+  </si>
+  <si>
+    <t>null#8499008, null#null, null#149514</t>
+  </si>
+  <si>
+    <t>prohibited</t>
   </si>
 </sst>
 </file>
@@ -229,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -272,139 +623,1644 @@
         <v>11</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="E2" t="s" s="2">
+      <c r="F2" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="F2" t="s" s="2">
-        <v>16</v>
-      </c>
       <c r="G2" t="s" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>22</v>
-      </c>
       <c r="F3" t="s" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
+      <c r="D7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="F5" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>14</v>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
